--- a/branches/dependabot/github_actions/dev/actions-d025328a43/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-d025328a43/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="559">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T01:49:31+00:00</t>
+    <t>2026-09-14T01:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -821,9 +821,6 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
-    <t>Art der Blutgruppenbestimmung</t>
-  </si>
-  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -1047,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Datum der Blutgruppenbestimmung</t>
+    <t>Nicht im Datensatz</t>
   </si>
   <si>
     <t>Observation.effective[x]:effectivePeriod</t>
@@ -1984,98 +1981,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2269,10 +2268,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2354,7 +2353,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>
@@ -5135,30 +5134,30 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5273,10 +5272,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5393,10 +5392,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5422,16 +5421,16 @@
         <v>146</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5478,7 +5477,7 @@
         <v>119</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5502,7 +5501,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5513,13 +5512,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
@@ -5544,16 +5543,16 @@
         <v>146</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5563,7 +5562,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5602,7 +5601,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5626,7 +5625,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5637,13 +5636,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5668,16 +5667,16 @@
         <v>146</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5687,7 +5686,7 @@
         <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>82</v>
@@ -5726,7 +5725,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5750,7 +5749,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5761,10 +5760,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5790,16 +5789,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5848,7 +5847,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5872,7 +5871,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5883,10 +5882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5909,19 +5908,19 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5970,7 +5969,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5985,19 +5984,19 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6005,10 +6004,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6031,16 +6030,16 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6090,7 +6089,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6114,10 +6113,10 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6125,14 +6124,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6151,19 +6150,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6212,7 +6211,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6230,16 +6229,16 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6247,14 +6246,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6273,19 +6272,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6322,17 +6321,17 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6350,16 +6349,16 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6367,16 +6366,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="B36" t="s" s="2">
+      <c r="D36" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6395,19 +6394,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6456,7 +6455,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6471,19 +6470,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6491,16 +6490,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="B37" t="s" s="2">
+      <c r="D37" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6519,19 +6518,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6580,7 +6579,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6598,16 +6597,16 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6615,10 +6614,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6644,13 +6643,13 @@
         <v>128</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6700,7 +6699,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6724,10 +6723,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6735,10 +6734,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6761,17 +6760,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6820,7 +6819,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6838,16 +6837,16 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6855,10 +6854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6884,16 +6883,16 @@
         <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6942,7 +6941,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6951,7 +6950,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6963,24 +6962,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7095,10 +7094,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7215,10 +7214,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7244,16 +7243,16 @@
         <v>146</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7282,13 +7281,13 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7298,7 +7297,7 @@
         <v>119</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7322,7 +7321,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7333,13 +7332,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7364,16 +7363,16 @@
         <v>146</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7422,7 +7421,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7446,7 +7445,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7457,10 +7456,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7575,10 +7574,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7695,10 +7694,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7724,16 +7723,16 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7743,46 +7742,46 @@
         <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7806,7 +7805,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7817,10 +7816,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7846,13 +7845,13 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7902,7 +7901,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7926,7 +7925,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7937,10 +7936,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7966,14 +7965,14 @@
         <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8022,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8046,7 +8045,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8057,10 +8056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8086,14 +8085,14 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8142,7 +8141,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8166,7 +8165,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8177,10 +8176,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8203,19 +8202,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8264,7 +8263,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8288,7 +8287,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8299,13 +8298,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
@@ -8330,16 +8329,16 @@
         <v>146</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8388,7 +8387,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8412,7 +8411,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8423,10 +8422,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8541,10 +8540,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8661,10 +8660,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8690,16 +8689,16 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8709,7 +8708,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8748,7 +8747,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8772,7 +8771,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8783,10 +8782,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8812,13 +8811,13 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8868,7 +8867,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8892,7 +8891,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8903,10 +8902,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8932,14 +8931,14 @@
         <v>168</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8988,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9012,7 +9011,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9023,10 +9022,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9052,14 +9051,14 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9108,7 +9107,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9132,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9143,10 +9142,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9169,19 +9168,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9230,7 +9229,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9254,7 +9253,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9265,10 +9264,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9294,16 +9293,16 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9352,7 +9351,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9376,7 +9375,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9387,10 +9386,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9416,16 +9415,16 @@
         <v>236</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9453,11 +9452,11 @@
         <v>150</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9474,7 +9473,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9483,7 +9482,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9498,7 +9497,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9509,14 +9508,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9538,16 +9537,16 @@
         <v>236</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9575,11 +9574,11 @@
         <v>150</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9596,7 +9595,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9617,24 +9616,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9657,19 +9656,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9718,7 +9717,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9742,7 +9741,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9753,10 +9752,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9782,13 +9781,13 @@
         <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9817,11 +9816,11 @@
         <v>158</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9838,7 +9837,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9859,24 +9858,24 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9902,16 +9901,16 @@
         <v>236</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9939,11 +9938,11 @@
         <v>158</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9960,7 +9959,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9984,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9995,10 +9994,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10021,16 +10020,16 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10080,7 +10079,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10101,24 +10100,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10141,16 +10140,16 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10200,7 +10199,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10221,24 +10220,24 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10261,19 +10260,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10322,7 +10321,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10334,19 +10333,19 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10357,10 +10356,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10475,10 +10474,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10595,14 +10594,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10624,10 +10623,10 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>116</v>
@@ -10682,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10717,10 +10716,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10743,13 +10742,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10800,7 +10799,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10809,7 +10808,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -10824,7 +10823,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10835,10 +10834,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10861,13 +10860,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10918,7 +10917,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10927,7 +10926,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10942,7 +10941,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10953,10 +10952,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10982,16 +10981,16 @@
         <v>236</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11019,11 +11018,11 @@
         <v>172</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>504</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11061,10 +11060,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11075,10 +11074,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11104,16 +11103,16 @@
         <v>236</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11141,11 +11140,11 @@
         <v>158</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11162,7 +11161,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11183,10 +11182,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11197,10 +11196,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11223,17 +11222,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11282,7 +11281,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11317,10 +11316,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11346,10 +11345,10 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11400,7 +11399,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11424,7 +11423,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11435,10 +11434,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11461,16 +11460,16 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11520,7 +11519,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11544,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11555,10 +11554,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11581,16 +11580,16 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11640,7 +11639,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11664,7 +11663,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11675,10 +11674,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11701,19 +11700,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11762,7 +11761,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11786,7 +11785,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11797,10 +11796,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11915,10 +11914,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12035,14 +12034,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12064,10 +12063,10 @@
         <v>113</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>116</v>
@@ -12122,7 +12121,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12157,10 +12156,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12186,13 +12185,13 @@
         <v>236</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>253</v>
@@ -12244,7 +12243,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>93</v>
@@ -12265,13 +12264,13 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -12279,10 +12278,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12305,19 +12304,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>550</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12366,7 +12365,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12387,24 +12386,24 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12430,16 +12429,16 @@
         <v>236</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>555</v>
-      </c>
       <c r="O86" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12467,11 +12466,11 @@
         <v>150</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12488,7 +12487,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12497,7 +12496,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12512,7 +12511,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12523,14 +12522,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12552,16 +12551,16 @@
         <v>236</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12589,11 +12588,11 @@
         <v>150</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12610,7 +12609,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12631,24 +12630,24 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12674,16 +12673,16 @@
         <v>83</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="N88" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O88" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12732,7 +12731,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12756,7 +12755,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
